--- a/out/Attention_Base_repeat_3_000002.xlsx
+++ b/out/Attention_Base_repeat_3_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention_Base_repeat_3_000002.xlsx
+++ b/out/Attention_Base_repeat_3_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01108091417700052</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.0251281876116991</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.02428077533841133</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.02077604830265045</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.02164752036333084</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0207480825483799</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01868900470435619</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.02113918587565422</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.02824826911091805</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0284254401922226</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.02648035436868668</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.02374143898487091</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.02338464930653572</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.02200772985816002</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.02050960250198841</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01946247927844524</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01887226104736328</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01816200464963913</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01717893593013287</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01649181544780731</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01607833430171013</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01524987164884806</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01443439163267612</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01749046519398689</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01799578592181206</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01810479164123535</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01841907948255539</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01836862228810787</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01777592673897743</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01711739599704742</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01675771176815033</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01608320698142052</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01557748299092054</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01526510063558817</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01559486519545317</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01711454056203365</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0176431592553854</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01770847104489803</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01953049376606941</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02175991609692574</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.02562488242983818</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.03434781730175018</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.03943769633769989</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.09912116825580597</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.05764740705490112</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.05333904922008514</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.04906722903251648</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.05349123477935791</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.05010226368904114</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.06663287431001663</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.06442969292402267</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.06123329699039459</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.05715706199407578</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.05443885922431946</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.05698547512292862</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.05359490215778351</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.05357291549444199</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.05724122375249863</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.05672027170658112</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.05583183467388153</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.06021625548601151</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.05781985819339752</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.05525176972150803</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.05850182473659515</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.06316650658845901</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.06996075809001923</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.06774097681045532</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.06250582635402679</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.06094569712877274</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.05989521741867065</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.06002657115459442</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.05767607688903809</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.05802175402641296</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.05685262382030487</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.05475389957427979</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.05415612459182739</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.05404830724000931</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.05271973460912704</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.05172941088676453</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.05130316317081451</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.05108878761529922</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.05166541039943695</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.05052805691957474</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.05037038773298264</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.04960665851831436</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.04809439927339554</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.04893749207258224</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.04920180141925812</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.05214903503656387</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.04888655617833138</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.04839302971959114</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.04915778711438179</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.04716609790921211</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.04592201858758926</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.04503710195422173</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.04637976735830307</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.04482685029506683</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.04427695274353027</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.04337713867425919</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.04395825788378716</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.04219876602292061</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.04228939861059189</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.04232805222272873</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.041380874812603</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.04113074019551277</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.04057451337575912</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.03972342610359192</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.03920354694128036</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.03905408456921577</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.03835559636354446</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.03878204524517059</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.03776323422789574</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.03797516226768494</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.03743980079889297</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.03751811757683754</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.04050667583942413</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.04010040313005447</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.04629969596862793</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.04267915338277817</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.04504503682255745</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0424346849322319</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.04184738546609879</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.04229871928691864</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.04104376584291458</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.0436755046248436</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>
